--- a/3course/distributiveOperations/lab3/lab3.xlsx
+++ b/3course/distributiveOperations/lab3/lab3.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\uni\3course\distributiveOperations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\University\3course\distributiveOperations\lab3\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,28 +24,56 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
   <si>
     <t>Test Number</t>
   </si>
   <si>
-    <t>Matrix Size</t>
-  </si>
-  <si>
-    <t>Execution time (sec</t>
-  </si>
-  <si>
     <t>Basic Computational Operation Execution Time τ (sec):</t>
   </si>
   <si>
     <t>Theoretical time (sec)</t>
+  </si>
+  <si>
+    <t>Serial algorithm</t>
+  </si>
+  <si>
+    <t>Parallel algorithm</t>
+  </si>
+  <si>
+    <t>2 processors</t>
+  </si>
+  <si>
+    <t>4 processors</t>
+  </si>
+  <si>
+    <t>8 processors</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Speed Up</t>
+  </si>
+  <si>
+    <t>System Size</t>
+  </si>
+  <si>
+    <t>Execution time (sec)</t>
+  </si>
+  <si>
+    <t>(для 1500): τ =</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000\ _₴"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -54,8 +82,16 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -80,8 +116,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4CD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -104,11 +158,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -116,7 +207,40 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -405,120 +529,475 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:F11"/>
+  <dimension ref="C2:P14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" customWidth="1"/>
     <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" customWidth="1"/>
+    <col min="10" max="10" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C2" s="3" t="s">
+    <row r="2" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="H2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C3" s="1" t="s">
+      <c r="K2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+    </row>
+    <row r="3" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="7"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="L3" s="10"/>
+      <c r="M3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="N3" s="11"/>
+      <c r="O3" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="P3" s="10"/>
+    </row>
+    <row r="4" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C5" s="1">
         <v>1</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="F5" s="6">
+        <f>((2*D5*D5*D5)/3+(D5*D5))*$D$14</f>
+        <v>8.0052186332186342E-7</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1">
+        <v>10</v>
+      </c>
+      <c r="J5" s="3">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K5" s="4">
+        <v>8.1000000000000004E-5</v>
+      </c>
+      <c r="L5" s="3">
+        <f>J5/K5</f>
+        <v>0.1234567901234568</v>
+      </c>
+      <c r="M5" s="4">
+        <v>2.63E-4</v>
+      </c>
+      <c r="N5" s="3">
+        <f>J5/M5</f>
+        <v>3.8022813688212934E-2</v>
+      </c>
+      <c r="O5" s="4">
+        <v>1.255E-3</v>
+      </c>
+      <c r="P5" s="3">
+        <f>J5/O5</f>
+        <v>7.9681274900398405E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C6" s="1">
         <v>2</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="D6" s="2">
+        <v>100</v>
+      </c>
+      <c r="E6" s="1">
+        <v>1.39E-3</v>
+      </c>
+      <c r="F6" s="6">
+        <f t="shared" ref="F6:F12" si="0">((2*D6*D6*D6)/3+(D6*D6))*$D$14</f>
+        <v>7.0654755762755771E-4</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>100</v>
+      </c>
+      <c r="J6" s="3">
+        <v>1.39E-3</v>
+      </c>
+      <c r="K6" s="4">
+        <v>6.8900000000000005E-4</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" ref="L6:L12" si="1">J6/K6</f>
+        <v>2.0174165457184321</v>
+      </c>
+      <c r="M6" s="4">
+        <v>8.8400000000000002E-4</v>
+      </c>
+      <c r="N6" s="3">
+        <f t="shared" ref="N6:N12" si="2">J6/M6</f>
+        <v>1.5723981900452488</v>
+      </c>
+      <c r="O6" s="4">
+        <v>1.7099999999999999E-3</v>
+      </c>
+      <c r="P6" s="3">
+        <f t="shared" ref="P6:P12" si="3">J6/O6</f>
+        <v>0.8128654970760234</v>
+      </c>
+    </row>
+    <row r="7" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C7" s="1">
+        <v>3</v>
+      </c>
+      <c r="D7" s="2">
+        <v>500</v>
+      </c>
+      <c r="E7" s="1">
+        <v>8.6998000000000006E-2</v>
+      </c>
+      <c r="F7" s="6">
+        <f t="shared" si="0"/>
+        <v>8.7274285751285749E-2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1">
+        <v>500</v>
+      </c>
+      <c r="J7" s="3">
+        <v>8.6998000000000006E-2</v>
+      </c>
+      <c r="K7" s="4">
+        <v>4.5587999999999997E-2</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9083530753707119</v>
+      </c>
+      <c r="M7" s="4">
+        <v>3.1073E-2</v>
+      </c>
+      <c r="N7" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7997940334052074</v>
+      </c>
+      <c r="O7" s="4">
+        <v>3.1920999999999998E-2</v>
+      </c>
+      <c r="P7" s="3">
+        <f t="shared" si="3"/>
+        <v>2.7254158704301248</v>
+      </c>
+    </row>
+    <row r="8" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C8" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C4" s="1">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2">
-        <v>10</v>
-      </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="2">
-        <v>100</v>
-      </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C6" s="1">
-        <v>3</v>
-      </c>
-      <c r="D6" s="2">
-        <v>500</v>
-      </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C7" s="1">
+      <c r="D8" s="2">
+        <v>1000</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0.68412600000000001</v>
+      </c>
+      <c r="F8" s="6">
+        <f t="shared" si="0"/>
+        <v>0.69715012705812707</v>
+      </c>
+      <c r="H8" s="2">
         <v>4</v>
       </c>
-      <c r="D7" s="2">
+      <c r="I8" s="1">
         <v>1000</v>
       </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C8" s="1">
+      <c r="J8" s="3">
+        <v>0.68412600000000001</v>
+      </c>
+      <c r="K8" s="4">
+        <v>0.356767</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9175708515641863</v>
+      </c>
+      <c r="M8" s="4">
+        <v>0.250166</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="2"/>
+        <v>2.7346881670570742</v>
+      </c>
+      <c r="O8" s="4">
+        <v>0.21231</v>
+      </c>
+      <c r="P8" s="3">
+        <f t="shared" si="3"/>
+        <v>3.2222975837219163</v>
+      </c>
+    </row>
+    <row r="9" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C9" s="1">
         <v>5</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D9" s="2">
         <v>1500</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C9" s="1">
+      <c r="E9" s="1">
+        <v>2.3517070000000002</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" si="0"/>
+        <v>2.3517070000000002</v>
+      </c>
+      <c r="H9" s="2">
+        <v>5</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2.3517070000000002</v>
+      </c>
+      <c r="K9" s="4">
+        <v>1.230559</v>
+      </c>
+      <c r="L9" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9110883752831034</v>
+      </c>
+      <c r="M9" s="4">
+        <v>0.74536400000000003</v>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="2"/>
+        <v>3.1551121331322682</v>
+      </c>
+      <c r="O9" s="4">
+        <v>0.71411100000000005</v>
+      </c>
+      <c r="P9" s="3">
+        <f t="shared" si="3"/>
+        <v>3.2931953155741893</v>
+      </c>
+    </row>
+    <row r="10" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C10" s="1">
         <v>6</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D10" s="2">
         <v>2000</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="1">
+      <c r="E10" s="1">
+        <v>5.6237250000000003</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" si="0"/>
+        <v>5.5730243806563813</v>
+      </c>
+      <c r="H10" s="2">
+        <v>6</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>5.6237250000000003</v>
+      </c>
+      <c r="K10" s="4">
+        <v>2.9614210000000001</v>
+      </c>
+      <c r="L10" s="3">
+        <f t="shared" si="1"/>
+        <v>1.8989954484688263</v>
+      </c>
+      <c r="M10" s="4">
+        <v>1.845766</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="2"/>
+        <v>3.046824462039067</v>
+      </c>
+      <c r="O10" s="4">
+        <v>1.598341</v>
+      </c>
+      <c r="P10" s="3">
+        <f t="shared" si="3"/>
+        <v>3.5184763451603884</v>
+      </c>
+    </row>
+    <row r="11" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C11" s="1">
         <v>7</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D11" s="2">
         <v>2500</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="1">
+      <c r="E11" s="1">
+        <v>10.729335000000001</v>
+      </c>
+      <c r="F11" s="6">
+        <f t="shared" si="0"/>
+        <v>10.883181745106747</v>
+      </c>
+      <c r="H11" s="2">
+        <v>7</v>
+      </c>
+      <c r="I11" s="1">
+        <v>2500</v>
+      </c>
+      <c r="J11" s="3">
+        <v>10.729335000000001</v>
+      </c>
+      <c r="K11" s="4">
+        <v>5.7410100000000002</v>
+      </c>
+      <c r="L11" s="3">
+        <f t="shared" si="1"/>
+        <v>1.868893278360428</v>
+      </c>
+      <c r="M11" s="4">
+        <v>3.5895440000000001</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="2"/>
+        <v>2.9890523698831943</v>
+      </c>
+      <c r="O11" s="4">
+        <v>3.2046250000000001</v>
+      </c>
+      <c r="P11" s="3">
+        <f t="shared" si="3"/>
+        <v>3.3480781682724188</v>
+      </c>
+    </row>
+    <row r="12" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C12" s="1">
         <v>8</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D12" s="2">
         <v>3000</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="2"/>
+      <c r="E12" s="1">
+        <v>18.378240999999999</v>
+      </c>
+      <c r="F12" s="6">
+        <f t="shared" si="0"/>
+        <v>18.804258569430573</v>
+      </c>
+      <c r="H12" s="2">
+        <v>8</v>
+      </c>
+      <c r="I12" s="1">
+        <v>3000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>18.378240999999999</v>
+      </c>
+      <c r="K12" s="4">
+        <v>9.6209790000000002</v>
+      </c>
+      <c r="L12" s="3">
+        <f t="shared" si="1"/>
+        <v>1.9102256641449897</v>
+      </c>
+      <c r="M12" s="4">
+        <v>6.2175079999999996</v>
+      </c>
+      <c r="N12" s="3">
+        <f t="shared" si="2"/>
+        <v>2.9558853804450274</v>
+      </c>
+      <c r="O12" s="4">
+        <v>5.6511230000000001</v>
+      </c>
+      <c r="P12" s="3">
+        <f t="shared" si="3"/>
+        <v>3.2521396189748479</v>
+      </c>
+    </row>
+    <row r="14" spans="3:16" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5">
+        <f>E9/((2*D9*D9*D9)/3+(D9*D9))</f>
+        <v>1.0441589521589523E-9</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="C2:F2"/>
+  <mergeCells count="8">
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="K2:P2"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="O3:P3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
